--- a/research/traditional_assets/database/data/israel/israel_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.104</v>
+        <v>0.0863</v>
       </c>
       <c r="E2">
-        <v>0.374</v>
+        <v>0.141</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>44.2</v>
+        <v>41.1</v>
       </c>
       <c r="L2">
-        <v>0.2144590004852014</v>
+        <v>0.2027627035027134</v>
       </c>
       <c r="M2">
-        <v>16.4</v>
+        <v>18.5</v>
       </c>
       <c r="N2">
-        <v>0.07158446093408992</v>
+        <v>0.07344184200079397</v>
       </c>
       <c r="O2">
-        <v>0.3710407239819004</v>
+        <v>0.4501216545012166</v>
       </c>
       <c r="P2">
-        <v>16.4</v>
+        <v>18.5</v>
       </c>
       <c r="Q2">
-        <v>0.07158446093408992</v>
+        <v>0.07344184200079397</v>
       </c>
       <c r="R2">
-        <v>0.3710407239819004</v>
+        <v>0.4501216545012166</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>833.1</v>
+        <v>892</v>
       </c>
       <c r="V2">
-        <v>3.636403317328678</v>
+        <v>3.541087733227471</v>
       </c>
       <c r="W2">
-        <v>0.1294669009958992</v>
+        <v>0.121310507674144</v>
       </c>
       <c r="X2">
-        <v>0.1527238140774585</v>
+        <v>0.1174586386227311</v>
       </c>
       <c r="Y2">
-        <v>-0.02325691308155928</v>
+        <v>0.003851869051412923</v>
       </c>
       <c r="Z2">
-        <v>1.448348559381589</v>
+        <v>0.7228958630527818</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06809265105042021</v>
+        <v>0.05843315113089307</v>
       </c>
       <c r="AC2">
-        <v>-0.06809265105042021</v>
+        <v>-0.05843315113089307</v>
       </c>
       <c r="AD2">
-        <v>774.7</v>
+        <v>833.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>774.7</v>
+        <v>833.7</v>
       </c>
       <c r="AG2">
-        <v>-58.39999999999998</v>
+        <v>-58.29999999999995</v>
       </c>
       <c r="AH2">
-        <v>0.7717672843195855</v>
+        <v>0.7679624170965365</v>
       </c>
       <c r="AI2">
-        <v>0.6898486197684773</v>
+        <v>0.705031712473573</v>
       </c>
       <c r="AJ2">
-        <v>-0.3421206795547743</v>
+        <v>-0.3011363636363633</v>
       </c>
       <c r="AK2">
-        <v>-0.2014487754398067</v>
+        <v>-0.2006884681583475</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.104</v>
+        <v>0.0863</v>
       </c>
       <c r="E3">
-        <v>0.374</v>
+        <v>0.141</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>44.2</v>
+        <v>41.1</v>
       </c>
       <c r="L3">
-        <v>0.2144590004852014</v>
+        <v>0.2027627035027134</v>
       </c>
       <c r="M3">
-        <v>16.4</v>
+        <v>18.5</v>
       </c>
       <c r="N3">
-        <v>0.07158446093408992</v>
+        <v>0.07344184200079397</v>
       </c>
       <c r="O3">
-        <v>0.3710407239819004</v>
+        <v>0.4501216545012166</v>
       </c>
       <c r="P3">
-        <v>16.4</v>
+        <v>18.5</v>
       </c>
       <c r="Q3">
-        <v>0.07158446093408992</v>
+        <v>0.07344184200079397</v>
       </c>
       <c r="R3">
-        <v>0.3710407239819004</v>
+        <v>0.4501216545012166</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>833.1</v>
+        <v>892</v>
       </c>
       <c r="V3">
-        <v>3.636403317328678</v>
+        <v>3.541087733227471</v>
       </c>
       <c r="W3">
-        <v>0.1294669009958992</v>
+        <v>0.121310507674144</v>
       </c>
       <c r="X3">
-        <v>0.1527238140774585</v>
+        <v>0.1174586386227311</v>
       </c>
       <c r="Y3">
-        <v>-0.02325691308155928</v>
+        <v>0.003851869051412923</v>
       </c>
       <c r="Z3">
-        <v>1.448348559381589</v>
+        <v>0.7228958630527818</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06809265105042021</v>
+        <v>0.05843315113089307</v>
       </c>
       <c r="AC3">
-        <v>-0.06809265105042021</v>
+        <v>-0.05843315113089307</v>
       </c>
       <c r="AD3">
-        <v>774.7</v>
+        <v>833.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>774.7</v>
+        <v>833.7</v>
       </c>
       <c r="AG3">
-        <v>-58.39999999999998</v>
+        <v>-58.29999999999995</v>
       </c>
       <c r="AH3">
-        <v>0.7717672843195855</v>
+        <v>0.7679624170965365</v>
       </c>
       <c r="AI3">
-        <v>0.6898486197684773</v>
+        <v>0.705031712473573</v>
       </c>
       <c r="AJ3">
-        <v>-0.3421206795547743</v>
+        <v>-0.3011363636363633</v>
       </c>
       <c r="AK3">
-        <v>-0.2014487754398067</v>
+        <v>-0.2006884681583475</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/israel/israel_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0863</v>
+        <v>0.101</v>
       </c>
       <c r="E2">
-        <v>0.141</v>
+        <v>0.215</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>41.1</v>
+        <v>5694</v>
       </c>
       <c r="L2">
-        <v>0.2027627035027134</v>
+        <v>0.3715546043015244</v>
       </c>
       <c r="M2">
-        <v>18.5</v>
+        <v>1639.4</v>
       </c>
       <c r="N2">
-        <v>0.07344184200079397</v>
+        <v>0.03865670656367015</v>
       </c>
       <c r="O2">
-        <v>0.4501216545012166</v>
+        <v>0.2879171057253249</v>
       </c>
       <c r="P2">
-        <v>18.5</v>
+        <v>1418.5</v>
       </c>
       <c r="Q2">
-        <v>0.07344184200079397</v>
+        <v>0.03344793110928761</v>
       </c>
       <c r="R2">
-        <v>0.4501216545012166</v>
+        <v>0.2491218826835265</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>220.9</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1347444186897645</v>
       </c>
       <c r="U2">
-        <v>892</v>
+        <v>82075.39999999999</v>
       </c>
       <c r="V2">
-        <v>3.541087733227471</v>
+        <v>1.935320637974779</v>
       </c>
       <c r="W2">
-        <v>0.121310507674144</v>
+        <v>0.1601214421252372</v>
       </c>
       <c r="X2">
-        <v>0.1174586386227311</v>
+        <v>0.09210417316188488</v>
       </c>
       <c r="Y2">
-        <v>0.003851869051412923</v>
+        <v>0.06801726896335231</v>
       </c>
       <c r="Z2">
-        <v>0.7228958630527818</v>
+        <v>0.9212162015941906</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05843315113089307</v>
+        <v>0.07329594847590695</v>
       </c>
       <c r="AC2">
-        <v>-0.05843315113089307</v>
+        <v>-0.07329594847590695</v>
       </c>
       <c r="AD2">
-        <v>833.7</v>
+        <v>45852.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>833.7</v>
+        <v>45852.4</v>
       </c>
       <c r="AG2">
-        <v>-58.29999999999995</v>
+        <v>-36222.99999999999</v>
       </c>
       <c r="AH2">
-        <v>0.7679624170965365</v>
+        <v>0.5195056513818014</v>
       </c>
       <c r="AI2">
-        <v>0.705031712473573</v>
+        <v>0.5328031531929333</v>
       </c>
       <c r="AJ2">
-        <v>-0.3011363636363633</v>
+        <v>-5.855452458698388</v>
       </c>
       <c r="AK2">
-        <v>-0.2006884681583475</v>
+        <v>-9.093487975096629</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of Jerusalem Ltd. (TASE:JBNK)</t>
+          <t>Bank Hapoalim B.M. (TASE:POLI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0863</v>
+        <v>0.1</v>
       </c>
       <c r="E3">
-        <v>0.141</v>
+        <v>0.254</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,90 +728,334 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>41.1</v>
+        <v>2109.6</v>
       </c>
       <c r="L3">
-        <v>0.2027627035027134</v>
+        <v>0.379704458323584</v>
       </c>
       <c r="M3">
-        <v>18.5</v>
+        <v>633.8</v>
       </c>
       <c r="N3">
-        <v>0.07344184200079397</v>
+        <v>0.03950755804893252</v>
       </c>
       <c r="O3">
-        <v>0.4501216545012166</v>
+        <v>0.3004361016306409</v>
       </c>
       <c r="P3">
-        <v>18.5</v>
+        <v>566.5</v>
       </c>
       <c r="Q3">
-        <v>0.07344184200079397</v>
+        <v>0.0353124513012311</v>
       </c>
       <c r="R3">
-        <v>0.4501216545012166</v>
+        <v>0.2685343193022374</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>67.29999999999995</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.1061849163774061</v>
       </c>
       <c r="U3">
-        <v>892</v>
+        <v>31011.5</v>
       </c>
       <c r="V3">
-        <v>3.541087733227471</v>
+        <v>1.93308399563659</v>
       </c>
       <c r="W3">
-        <v>0.121310507674144</v>
+        <v>0.1601214421252372</v>
       </c>
       <c r="X3">
-        <v>0.1174586386227311</v>
+        <v>0.09006757252129328</v>
       </c>
       <c r="Y3">
-        <v>0.003851869051412923</v>
+        <v>0.0700538696039439</v>
       </c>
       <c r="Z3">
-        <v>0.7228958630527818</v>
+        <v>0.8754274009296462</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05843315113089307</v>
+        <v>0.07319412865565027</v>
       </c>
       <c r="AC3">
-        <v>-0.05843315113089307</v>
+        <v>-0.07319412865565027</v>
       </c>
       <c r="AD3">
-        <v>833.7</v>
+        <v>15401</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>833.7</v>
+        <v>15401</v>
       </c>
       <c r="AG3">
-        <v>-58.29999999999995</v>
+        <v>-15610.5</v>
       </c>
       <c r="AH3">
-        <v>0.7679624170965365</v>
+        <v>0.4897991635791181</v>
       </c>
       <c r="AI3">
-        <v>0.705031712473573</v>
+        <v>0.5004110252236269</v>
       </c>
       <c r="AJ3">
-        <v>-0.3011363636363633</v>
+        <v>-36.13541666666666</v>
       </c>
       <c r="AK3">
-        <v>-0.2006884681583475</v>
+        <v>66.48424190800702</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bank Leumi le-Israel B.M. (TASE:LUMI)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.101</v>
+      </c>
+      <c r="E4">
+        <v>0.215</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>2467.7</v>
+      </c>
+      <c r="L4">
+        <v>0.4261856239853545</v>
+      </c>
+      <c r="M4">
+        <v>754.3000000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.0420923990379518</v>
+      </c>
+      <c r="O4">
+        <v>0.3056692466669369</v>
+      </c>
+      <c r="P4">
+        <v>600.7</v>
+      </c>
+      <c r="Q4">
+        <v>0.03352101829788897</v>
+      </c>
+      <c r="R4">
+        <v>0.2434250516675447</v>
+      </c>
+      <c r="S4">
+        <v>153.6</v>
+      </c>
+      <c r="T4">
+        <v>0.2036325069600955</v>
+      </c>
+      <c r="U4">
+        <v>35665.9</v>
+      </c>
+      <c r="V4">
+        <v>1.99027349177739</v>
+      </c>
+      <c r="W4">
+        <v>0.1792201378448846</v>
+      </c>
+      <c r="X4">
+        <v>0.09210417316188488</v>
+      </c>
+      <c r="Y4">
+        <v>0.08711596468299967</v>
+      </c>
+      <c r="Z4">
+        <v>0.7414587921938226</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.07329594847590695</v>
+      </c>
+      <c r="AC4">
+        <v>-0.07329594847590695</v>
+      </c>
+      <c r="AD4">
+        <v>19065.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>19065.7</v>
+      </c>
+      <c r="AG4">
+        <v>-16600.2</v>
+      </c>
+      <c r="AH4">
+        <v>0.5154870247500392</v>
+      </c>
+      <c r="AI4">
+        <v>0.5404538908983707</v>
+      </c>
+      <c r="AJ4">
+        <v>-12.57686188347604</v>
+      </c>
+      <c r="AK4">
+        <v>42.706971957808</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Israel Discount Bank Limited (TASE:DSCT)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.105</v>
+      </c>
+      <c r="E5">
+        <v>0.195</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1116.7</v>
+      </c>
+      <c r="L5">
+        <v>0.2806695654359465</v>
+      </c>
+      <c r="M5">
+        <v>251.3</v>
+      </c>
+      <c r="N5">
+        <v>0.02975161603485426</v>
+      </c>
+      <c r="O5">
+        <v>0.2250380585654159</v>
+      </c>
+      <c r="P5">
+        <v>251.3</v>
+      </c>
+      <c r="Q5">
+        <v>0.02975161603485426</v>
+      </c>
+      <c r="R5">
+        <v>0.2250380585654159</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>15398</v>
+      </c>
+      <c r="V5">
+        <v>1.822982028271731</v>
+      </c>
+      <c r="W5">
+        <v>0.1542062527618206</v>
+      </c>
+      <c r="X5">
+        <v>0.09767084045726442</v>
+      </c>
+      <c r="Y5">
+        <v>0.05653541230455618</v>
+      </c>
+      <c r="Z5">
+        <v>1.604508609912489</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.0735282699710441</v>
+      </c>
+      <c r="AC5">
+        <v>-0.0735282699710441</v>
+      </c>
+      <c r="AD5">
+        <v>11385.7</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>11385.7</v>
+      </c>
+      <c r="AG5">
+        <v>-4012.299999999999</v>
+      </c>
+      <c r="AH5">
+        <v>0.5740988185939099</v>
+      </c>
+      <c r="AI5">
+        <v>0.5691455593379622</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.9048327808222263</v>
+      </c>
+      <c r="AK5">
+        <v>-0.8709327313377755</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/israel/israel_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.101</v>
+        <v>0.1015</v>
       </c>
       <c r="E2">
-        <v>0.215</v>
+        <v>0.205</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>5694</v>
+        <v>5736.099999999999</v>
       </c>
       <c r="L2">
-        <v>0.3715546043015244</v>
+        <v>0.3689996783531682</v>
       </c>
       <c r="M2">
-        <v>1639.4</v>
+        <v>1649.8</v>
       </c>
       <c r="N2">
-        <v>0.03865670656367015</v>
+        <v>0.03859136150454381</v>
       </c>
       <c r="O2">
-        <v>0.2879171057253249</v>
+        <v>0.2876170220184446</v>
       </c>
       <c r="P2">
-        <v>1418.5</v>
+        <v>1428.9</v>
       </c>
       <c r="Q2">
-        <v>0.03344793110928761</v>
+        <v>0.03342417047753828</v>
       </c>
       <c r="R2">
-        <v>0.2491218826835265</v>
+        <v>0.2491065357995851</v>
       </c>
       <c r="S2">
         <v>220.9</v>
       </c>
       <c r="T2">
-        <v>0.1347444186897645</v>
+        <v>0.1338950175778882</v>
       </c>
       <c r="U2">
-        <v>82075.39999999999</v>
+        <v>83448.10000000001</v>
       </c>
       <c r="V2">
-        <v>1.935320637974779</v>
+        <v>1.951979509011591</v>
       </c>
       <c r="W2">
-        <v>0.1601214421252372</v>
+        <v>0.1571638474435289</v>
       </c>
       <c r="X2">
-        <v>0.09210417316188488</v>
+        <v>0.09487422562647083</v>
       </c>
       <c r="Y2">
-        <v>0.06801726896335231</v>
+        <v>0.06228962181705808</v>
       </c>
       <c r="Z2">
-        <v>0.9212162015941906</v>
+        <v>0.9189579035108979</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07329594847590695</v>
+        <v>0.07340608560409202</v>
       </c>
       <c r="AC2">
-        <v>-0.07329594847590695</v>
+        <v>-0.07340608560409202</v>
       </c>
       <c r="AD2">
-        <v>45852.4</v>
+        <v>46628.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>45852.4</v>
+        <v>46628.5</v>
       </c>
       <c r="AG2">
-        <v>-36222.99999999999</v>
+        <v>-36819.60000000001</v>
       </c>
       <c r="AH2">
-        <v>0.5195056513818014</v>
+        <v>0.5216941339688294</v>
       </c>
       <c r="AI2">
-        <v>0.5328031531929333</v>
+        <v>0.5345539546571775</v>
       </c>
       <c r="AJ2">
-        <v>-5.855452458698388</v>
+        <v>-6.208096578934065</v>
       </c>
       <c r="AK2">
-        <v>-9.093487975096629</v>
+        <v>-9.738831433332461</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -767,10 +767,10 @@
         <v>0.1601214421252372</v>
       </c>
       <c r="X3">
-        <v>0.09006757252129328</v>
+        <v>0.09005559542621495</v>
       </c>
       <c r="Y3">
-        <v>0.0700538696039439</v>
+        <v>0.07006584669902223</v>
       </c>
       <c r="Z3">
         <v>0.8754274009296462</v>
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07319412865565027</v>
+        <v>0.07318801793172341</v>
       </c>
       <c r="AC3">
-        <v>-0.07319412865565027</v>
+        <v>-0.07318801793172341</v>
       </c>
       <c r="AD3">
         <v>15401</v>
@@ -889,10 +889,10 @@
         <v>0.1792201378448846</v>
       </c>
       <c r="X4">
-        <v>0.09210417316188488</v>
+        <v>0.09209164504134661</v>
       </c>
       <c r="Y4">
-        <v>0.08711596468299967</v>
+        <v>0.08712849280353795</v>
       </c>
       <c r="Z4">
         <v>0.7414587921938226</v>
@@ -901,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07329594847590695</v>
+        <v>0.07328987843895066</v>
       </c>
       <c r="AC4">
-        <v>-0.07329594847590695</v>
+        <v>-0.07328987843895066</v>
       </c>
       <c r="AD4">
         <v>19065.7</v>
@@ -1011,10 +1011,10 @@
         <v>0.1542062527618206</v>
       </c>
       <c r="X5">
-        <v>0.09767084045726442</v>
+        <v>0.09765680621159506</v>
       </c>
       <c r="Y5">
-        <v>0.05653541230455618</v>
+        <v>0.05654944655022554</v>
       </c>
       <c r="Z5">
         <v>1.604508609912489</v>
@@ -1023,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0735282699710441</v>
+        <v>0.07352229276923339</v>
       </c>
       <c r="AC5">
-        <v>-0.0735282699710441</v>
+        <v>-0.07352229276923339</v>
       </c>
       <c r="AD5">
         <v>11385.7</v>
@@ -1056,6 +1056,128 @@
         <v>0</v>
       </c>
       <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bank of Jerusalem Ltd. (TASE:JBNK)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.102</v>
+      </c>
+      <c r="E6">
+        <v>0.185</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>42.1</v>
+      </c>
+      <c r="L6">
+        <v>0.1911898274296095</v>
+      </c>
+      <c r="M6">
+        <v>10.4</v>
+      </c>
+      <c r="N6">
+        <v>0.03047172575446821</v>
+      </c>
+      <c r="O6">
+        <v>0.2470308788598575</v>
+      </c>
+      <c r="P6">
+        <v>10.4</v>
+      </c>
+      <c r="Q6">
+        <v>0.03047172575446821</v>
+      </c>
+      <c r="R6">
+        <v>0.2470308788598575</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1372.7</v>
+      </c>
+      <c r="V6">
+        <v>4.02197480222678</v>
+      </c>
+      <c r="W6">
+        <v>0.1242621015348288</v>
+      </c>
+      <c r="X6">
+        <v>0.1157999818683626</v>
+      </c>
+      <c r="Y6">
+        <v>0.008462119666466233</v>
+      </c>
+      <c r="Z6">
+        <v>0.7850267379679144</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.07474868912847071</v>
+      </c>
+      <c r="AC6">
+        <v>-0.07474868912847071</v>
+      </c>
+      <c r="AD6">
+        <v>776.1</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>776.1</v>
+      </c>
+      <c r="AG6">
+        <v>-596.6</v>
+      </c>
+      <c r="AH6">
+        <v>0.6945587972078038</v>
+      </c>
+      <c r="AI6">
+        <v>0.6633333333333333</v>
+      </c>
+      <c r="AJ6">
+        <v>2.336858597728163</v>
+      </c>
+      <c r="AK6">
+        <v>2.943265910212136</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
         <v>0</v>
       </c>
     </row>
